--- a/data/trans_camb/P05A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P05A_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-11,71</t>
+          <t>-11,11</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,67</t>
+          <t>-8,66</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-10,58</t>
+          <t>-10,03</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 12,33</t>
+          <t>0,73; 12,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 11,94</t>
+          <t>0,21; 12,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,75; -3,84</t>
+          <t>-17,81; -3,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 9,61</t>
+          <t>-3,37; 9,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 6,32</t>
+          <t>-6,37; 6,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,19; -0,57</t>
+          <t>-16,17; -0,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 8,98</t>
+          <t>1,09; 9,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 7,38</t>
+          <t>-0,76; 7,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,42; -5,22</t>
+          <t>-15,01; -4,33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-40,04%</t>
+          <t>-38,0%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-25,79%</t>
+          <t>-25,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-33,73%</t>
+          <t>-31,97%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 46,79</t>
+          <t>3,26; 49,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 45,43</t>
+          <t>0,39; 47,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,56; -13,37</t>
+          <t>-57,6; -12,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 31,38</t>
+          <t>-9,29; 29,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 20,64</t>
+          <t>-17,16; 20,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,25; -1,55</t>
+          <t>-45,42; -1,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 30,78</t>
+          <t>3,34; 32,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 25,16</t>
+          <t>-2,22; 26,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,83; -17,3</t>
+          <t>-45,64; -14,38</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-10,44</t>
+          <t>-9,5</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-14,22</t>
+          <t>-11,62</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-12,16</t>
+          <t>-10,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 16,79</t>
+          <t>6,62; 17,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 14,23</t>
+          <t>3,66; 13,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,22; -4,32</t>
+          <t>-14,95; -4,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 11,41</t>
+          <t>0,42; 11,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 12,14</t>
+          <t>1,02; 11,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,39; -8,79</t>
+          <t>-17,55; -6,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 12,63</t>
+          <t>5,68; 13,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 11,87</t>
+          <t>4,38; 11,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,02; -8,09</t>
+          <t>-14,01; -6,25</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-37,37%</t>
+          <t>-34,02%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-44,6%</t>
+          <t>-36,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-40,88%</t>
+          <t>-34,88%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,79; 66,67</t>
+          <t>21,28; 66,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,28; 55,29</t>
+          <t>12,14; 53,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-54,12; -16,21</t>
+          <t>-50,48; -14,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 38,41</t>
+          <t>1,34; 41,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 42,04</t>
+          <t>2,99; 41,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,82; -29,48</t>
+          <t>-51,81; -21,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,3; 44,98</t>
+          <t>17,72; 46,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 42,96</t>
+          <t>13,93; 40,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,48; -28,87</t>
+          <t>-45,31; -22,53</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-8,8</t>
+          <t>-8,83</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-19,43</t>
+          <t>-16,91</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-14,34</t>
+          <t>-13,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 13,69</t>
+          <t>2,69; 13,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 7,93</t>
+          <t>-1,84; 8,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; -3,17</t>
+          <t>-14,18; -3,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 8,29</t>
+          <t>-1,94; 9,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 5,35</t>
+          <t>-5,41; 5,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,69; -14,91</t>
+          <t>-21,57; -12,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,46</t>
+          <t>1,76; 9,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 5,52</t>
+          <t>-1,91; 5,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,46; -10,8</t>
+          <t>-16,43; -9,7</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-29,39%</t>
+          <t>-29,49%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-51,74%</t>
+          <t>-45,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-42,29%</t>
+          <t>-38,41%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,27; 50,69</t>
+          <t>8,33; 49,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 29,21</t>
+          <t>-5,99; 29,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,05; -12,22</t>
+          <t>-43,75; -13,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 23,55</t>
+          <t>-4,75; 25,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 15,36</t>
+          <t>-13,34; 16,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,67; -42,16</t>
+          <t>-53,38; -35,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,54; 29,53</t>
+          <t>4,8; 29,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 16,58</t>
+          <t>-5,51; 16,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,15; -33,27</t>
+          <t>-46,35; -30,03</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-16,9</t>
+          <t>-11,68</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-15,38</t>
+          <t>-14,18</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-16,39</t>
+          <t>-12,92</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,15</t>
+          <t>1,45; 13,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 12,33</t>
+          <t>-0,01; 12,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-28,29; -9,06</t>
+          <t>-16,64; -5,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 13,99</t>
+          <t>1,9; 13,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 9,82</t>
+          <t>-2,01; 8,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,84; -10,04</t>
+          <t>-18,72; -9,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,0</t>
+          <t>3,85; 11,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 9,15</t>
+          <t>0,94; 9,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-24,55; -11,8</t>
+          <t>-16,24; -9,16</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-51,84%</t>
+          <t>-35,82%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-43,07%</t>
+          <t>-39,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-47,99%</t>
+          <t>-37,82%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,17; 44,35</t>
+          <t>4,3; 46,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 41,27</t>
+          <t>-0,17; 41,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,56; -28,98</t>
+          <t>-46,78; -19,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,69; 43,47</t>
+          <t>5,13; 42,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 29,63</t>
+          <t>-5,28; 26,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,87; -31,72</t>
+          <t>-48,41; -28,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,15; 37,5</t>
+          <t>10,67; 37,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 28,65</t>
+          <t>2,45; 28,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,81; -35,18</t>
+          <t>-44,45; -29,06</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-13,91</t>
+          <t>-14,14</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-15,82</t>
+          <t>-15,53</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-14,96</t>
+          <t>-14,9</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,2; 20,01</t>
+          <t>6,74; 20,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 13,46</t>
+          <t>-0,44; 13,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,76; -8,71</t>
+          <t>-20,0; -8,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 9,22</t>
+          <t>-4,55; 9,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 7,14</t>
+          <t>-5,83; 7,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-21,21; -10,78</t>
+          <t>-20,97; -10,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,29; 12,97</t>
+          <t>2,85; 12,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 8,3</t>
+          <t>-1,18; 8,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-18,49; -11,24</t>
+          <t>-18,67; -11,03</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-45,91%</t>
+          <t>-46,67%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-43,11%</t>
+          <t>-42,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-44,58%</t>
+          <t>-44,41%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>18,09; 74,76</t>
+          <t>20,4; 75,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,23; 50,12</t>
+          <t>-0,98; 49,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,54; -31,64</t>
+          <t>-58,03; -33,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 27,44</t>
+          <t>-11,33; 27,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 21,54</t>
+          <t>-14,3; 23,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,48; -32,01</t>
+          <t>-51,73; -31,41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,02; 42,1</t>
+          <t>7,89; 38,22</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 26,54</t>
+          <t>-3,29; 27,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-51,33; -36,24</t>
+          <t>-51,41; -35,76</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-10,02</t>
+          <t>-9,8</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,98</t>
+          <t>-16,01</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>-13,16</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>8,5; 23,99</t>
+          <t>9,11; 24,81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,17; 18,36</t>
+          <t>3,44; 18,66</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,24; -4,08</t>
+          <t>-15,14; -3,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 12,63</t>
+          <t>-2,02; 13,56</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 9,61</t>
+          <t>-5,08; 10,11</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 43,08</t>
+          <t>-21,7; -10,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,94; 16,01</t>
+          <t>5,37; 15,8</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,58; 11,21</t>
+          <t>1,23; 11,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 35,59</t>
+          <t>-17,52; -9,55</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-36,34%</t>
+          <t>-35,55%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>-47,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>-42,39%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>27,18; 99,76</t>
+          <t>28,81; 105,41</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12,86; 75,3</t>
+          <t>10,26; 76,22</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-50,95; -17,62</t>
+          <t>-48,88; -16,79</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 40,75</t>
+          <t>-5,17; 44,79</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 30,72</t>
+          <t>-13,45; 33,97</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-52,69; 145,46</t>
+          <t>-57,09; -33,64</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,19; 55,76</t>
+          <t>16,4; 55,51</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1,76; 38,79</t>
+          <t>3,61; 39,53</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-47,23; 123,81</t>
+          <t>-51,39; -32,5</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-13,63</t>
+          <t>-13,59</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-13,77</t>
+          <t>-13,39</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-13,73</t>
+          <t>-13,49</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,43; 17,72</t>
+          <t>0,11; 17,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 9,06</t>
+          <t>-7,54; 9,28</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-20,13; -6,82</t>
+          <t>-21,04; -6,71</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,03; 16,73</t>
+          <t>1,22; 16,14</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 8,39</t>
+          <t>-7,39; 7,64</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-19,34; -8,13</t>
+          <t>-20,02; -7,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,72; 14,12</t>
+          <t>3,7; 15,1</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 6,3</t>
+          <t>-4,52; 6,04</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -9,41</t>
+          <t>-18,26; -9,07</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-48,45%</t>
+          <t>-48,32%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-46,86%</t>
+          <t>-45,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-47,5%</t>
+          <t>-46,67%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>1,29; 76,07</t>
+          <t>0,93; 77,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 38,5</t>
+          <t>-22,65; 39,9</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-61,78; -28,54</t>
+          <t>-62,67; -28,03</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6,23; 67,26</t>
+          <t>4,38; 62,69</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 33,19</t>
+          <t>-22,56; 29,27</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-57,51; -31,01</t>
+          <t>-57,62; -30,86</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,93; 54,64</t>
+          <t>11,47; 58,73</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 24,8</t>
+          <t>-14,77; 23,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-57,1; -36,49</t>
+          <t>-55,94; -35,68</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-12,34</t>
+          <t>-10,97</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-10,83</t>
+          <t>-14,03</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-11,51</t>
+          <t>-12,51</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>7,9; 12,28</t>
+          <t>7,9; 12,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,6</t>
+          <t>4,22; 8,55</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -9,92</t>
+          <t>-13,09; -8,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,61</t>
+          <t>3,05; 7,64</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,41</t>
+          <t>0,02; 4,7</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 4,42</t>
+          <t>-16,05; -11,9</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,44</t>
+          <t>6,15; 9,57</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,79</t>
+          <t>2,57; 5,91</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-14,58; -2,81</t>
+          <t>-13,91; -11,09</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-41,79%</t>
+          <t>-37,16%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-31,46%</t>
+          <t>-40,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-35,96%</t>
+          <t>-39,09%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>25,96; 43,73</t>
+          <t>26,31; 43,88</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>13,43; 30,16</t>
+          <t>13,65; 30,0</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-54,14; -34,47</t>
+          <t>-43,31; -31,31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8,2; 22,51</t>
+          <t>8,59; 23,08</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 13,2</t>
+          <t>0,11; 14,36</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 13,33</t>
+          <t>-45,13; -36,02</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,72; 29,92</t>
+          <t>18,77; 30,56</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>8,15; 18,54</t>
+          <t>7,74; 18,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-45,53; -8,88</t>
+          <t>-42,38; -35,29</t>
         </is>
       </c>
     </row>
